--- a/virtual-physics-lab/app/dl/NJC_Q2a_cooling_readings.xlsx
+++ b/virtual-physics-lab/app/dl/NJC_Q2a_cooling_readings.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="7">
     <font>
       <name val="Calibri"/>
@@ -90,7 +92,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -99,6 +101,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -223,17 +226,18 @@
           </marker>
           <trendline>
             <trendlineType val="poly"/>
+            <order val="2"/>
             <dispRSqr val="1"/>
             <dispEq val="1"/>
           </trendline>
           <xVal>
             <numRef>
-              <f>'Suggested solution'!$A$6:$A$16</f>
+              <f>'Suggested solution'!$A$6:$A$15</f>
             </numRef>
           </xVal>
           <yVal>
             <numRef>
-              <f>'Suggested solution'!$B$6:$B$16</f>
+              <f>'Suggested solution'!$B$6:$B$15</f>
             </numRef>
           </yVal>
         </ser>
@@ -617,7 +621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -661,7 +665,7 @@
       <c r="A6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>80</v>
       </c>
     </row>
@@ -669,7 +673,7 @@
       <c r="A7" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>78.5</v>
       </c>
     </row>
@@ -677,7 +681,7 @@
       <c r="A8" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>78</v>
       </c>
     </row>
@@ -685,7 +689,7 @@
       <c r="A9" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>76.5</v>
       </c>
     </row>
@@ -693,7 +697,7 @@
       <c r="A10" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>75.5</v>
       </c>
     </row>
@@ -701,7 +705,7 @@
       <c r="A11" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>74.5</v>
       </c>
     </row>
@@ -709,7 +713,7 @@
       <c r="A12" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="6" t="n">
         <v>73.5</v>
       </c>
     </row>
@@ -717,7 +721,7 @@
       <c r="A13" s="5" t="n">
         <v>140</v>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="6" t="n">
         <v>72.5</v>
       </c>
     </row>
@@ -725,7 +729,7 @@
       <c r="A14" s="5" t="n">
         <v>160</v>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="6" t="n">
         <v>72</v>
       </c>
     </row>
@@ -733,16 +737,8 @@
       <c r="A15" s="5" t="n">
         <v>180</v>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="6" t="n">
         <v>70.5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>69.5</v>
       </c>
     </row>
   </sheetData>
@@ -756,7 +752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -811,7 +807,7 @@
       <c r="A6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>80</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -819,7 +815,7 @@
           <t>expected dθ/dt at 75 °C (model)</t>
         </is>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="7" t="n">
         <v>-0.0522</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -832,7 +828,7 @@
       <c r="A7" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B7" s="5" t="n">
+      <c r="B7" s="6" t="n">
         <v>78.5</v>
       </c>
     </row>
@@ -840,10 +836,10 @@
       <c r="A8" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="6" t="n">
         <v>78</v>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>The chart uses a polynomial trendline; its derivative at θ = 75 °C approximates the tangent gradient.</t>
         </is>
@@ -853,7 +849,7 @@
       <c r="A9" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="B9" s="5" t="n">
+      <c r="B9" s="6" t="n">
         <v>76.5</v>
       </c>
     </row>
@@ -861,7 +857,7 @@
       <c r="A10" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="B10" s="5" t="n">
+      <c r="B10" s="6" t="n">
         <v>75.5</v>
       </c>
     </row>
@@ -869,7 +865,7 @@
       <c r="A11" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="6" t="n">
         <v>74.5</v>
       </c>
     </row>
@@ -877,7 +873,7 @@
       <c r="A12" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="6" t="n">
         <v>73.5</v>
       </c>
     </row>
@@ -885,7 +881,7 @@
       <c r="A13" s="5" t="n">
         <v>140</v>
       </c>
-      <c r="B13" s="5" t="n">
+      <c r="B13" s="6" t="n">
         <v>72.5</v>
       </c>
     </row>
@@ -893,7 +889,7 @@
       <c r="A14" s="5" t="n">
         <v>160</v>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="6" t="n">
         <v>72</v>
       </c>
     </row>
@@ -901,16 +897,8 @@
       <c r="A15" s="5" t="n">
         <v>180</v>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="6" t="n">
         <v>70.5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>69.5</v>
       </c>
     </row>
   </sheetData>
